--- a/output/北塩原村_サービス見込量.xlsx
+++ b/output/北塩原村_サービス見込量.xlsx
@@ -3480,7 +3480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7118,15 +7118,312 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="40" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>13　短期入所（医療型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>※ 実績なし。医療的ケア者の利用が生じた場合に備える。圏域の供給を県に確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>増減要因</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度
+（基準）</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>継続利用者</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="19">
+        <f>C183</f>
+        <v/>
+      </c>
+      <c r="E176" s="19">
+        <f>D183</f>
+        <v/>
+      </c>
+      <c r="F176" s="19">
+        <f>E183</f>
+        <v/>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>前年度の利用者数を繰り越す</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>＋　特別支援学校卒業・18歳到達</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C177" s="20" t="n"/>
+      <c r="D177" s="18" t="n"/>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="18" t="n"/>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>02_年齢到達者一覧から転記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>＋　施設・病院からの地域移行</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="n"/>
+      <c r="D178" s="18" t="n"/>
+      <c r="E178" s="18" t="n"/>
+      <c r="F178" s="18" t="n"/>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>移行予定者を個別に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>＋　新規支給決定（相談・転入等）</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="n"/>
+      <c r="D179" s="18" t="n"/>
+      <c r="E179" s="18" t="n"/>
+      <c r="F179" s="18" t="n"/>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>相談支援事業所からの利用開始相談を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>－　65歳到達・介護保険移行</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C180" s="21" t="n"/>
+      <c r="D180" s="22" t="n"/>
+      <c r="E180" s="22" t="n"/>
+      <c r="F180" s="22" t="n"/>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>－　一般就労・サービス終了</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C181" s="21" t="n"/>
+      <c r="D181" s="22" t="n"/>
+      <c r="E181" s="22" t="n"/>
+      <c r="F181" s="22" t="n"/>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>就労移行支援からの一般就労等</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>－　死亡・転出・長期入院</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C182" s="21" t="n"/>
+      <c r="D182" s="22" t="n"/>
+      <c r="E182" s="22" t="n"/>
+      <c r="F182" s="22" t="n"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>高齢化が進む本村では主要な減少要因</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="23" t="inlineStr">
+        <is>
+          <t>＝　利用者数</t>
+        </is>
+      </c>
+      <c r="B183" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C183" s="25">
+        <f>C176</f>
+        <v/>
+      </c>
+      <c r="D183" s="25">
+        <f>D176+SUM(D177:D179)-SUM(D180:D182)</f>
+        <v/>
+      </c>
+      <c r="E183" s="25">
+        <f>E176+SUM(E177:E179)-SUM(E180:E182)</f>
+        <v/>
+      </c>
+      <c r="F183" s="25">
+        <f>F176+SUM(F177:F179)-SUM(F180:F182)</f>
+        <v/>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>継続＋流入－流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　1人当たり月利用量</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C184" s="26" t="n"/>
+      <c r="D184" s="26" t="n"/>
+      <c r="E184" s="26" t="n"/>
+      <c r="F184" s="26" t="n"/>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>利用者ごとの月間予定量の平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="23" t="inlineStr">
+        <is>
+          <t>＝　月間サービス量</t>
+        </is>
+      </c>
+      <c r="B185" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C185" s="27">
+        <f>ROUND(C183*C184,1)</f>
+        <v/>
+      </c>
+      <c r="D185" s="27">
+        <f>ROUND(D183*D184,1)</f>
+        <v/>
+      </c>
+      <c r="E185" s="27">
+        <f>ROUND(E183*E184,1)</f>
+        <v/>
+      </c>
+      <c r="F185" s="27">
+        <f>ROUND(F183*F184,1)</f>
+        <v/>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>利用者数×1人当たり月利用量</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>黄色は入力欄、緑は数式です。継続利用者は前年度の利用者数を自動で繰り越します。流出行はマイナスの人数ではなく、減少する人数を正の数で入力してください（表示は自動でマイナスになります）。令和8年度の基準人数は、村の支給決定者台帳による実利用者数に置き換えてください。現在入っているのは現行計画（第7期）の令和8年度見込量です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="A159:G159"/>
     <mergeCell ref="A131:G131"/>
     <mergeCell ref="A62:G62"/>
@@ -7142,7 +7439,9 @@
     <mergeCell ref="A132:G132"/>
     <mergeCell ref="A146:G146"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A187:G187"/>
     <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A174:G174"/>
     <mergeCell ref="A160:G160"/>
     <mergeCell ref="A75:G75"/>
     <mergeCell ref="A89:G89"/>
@@ -7165,7 +7464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8290,14 +8589,14 @@
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>5　医療型児童発達支援</t>
+          <t>5　障がい児相談支援</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>※ 児童発達支援へ一元化。実績なし</t>
+          <t>※ 令和7年度は請求8件</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8650,7 @@
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60" s="19">
         <f>C66</f>
@@ -8559,287 +8858,15 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>6　障がい児相談支援</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>※ 令和7年度は請求8件</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>増減要因</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>単位</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>令和8年度
-（基準）</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>継続利用者</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="19">
-        <f>C79</f>
-        <v/>
-      </c>
-      <c r="E73" s="19">
-        <f>D79</f>
-        <v/>
-      </c>
-      <c r="F73" s="19">
-        <f>E79</f>
-        <v/>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>前年度の利用者数を繰り越す</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>＋　新規支給決定（診断・転入等）</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>新規の発達相談・診断からの流入</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>＋　就学・進級による流入</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>児童発達支援から放課後等デイサービスへの移行等</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>－　就学による他サービスへの移行</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C76" s="21" t="n"/>
-      <c r="D76" s="22" t="n"/>
-      <c r="E76" s="22" t="n"/>
-      <c r="F76" s="22" t="n"/>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>児童発達支援からの流出</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>－　18歳到達・高校卒業による移行</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="22" t="n"/>
-      <c r="E77" s="22" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>－　転出・利用終了</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="22" t="n"/>
-      <c r="E78" s="22" t="n"/>
-      <c r="F78" s="22" t="n"/>
-      <c r="G78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>＝　利用者数</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C79" s="25">
-        <f>C73</f>
-        <v/>
-      </c>
-      <c r="D79" s="25">
-        <f>D73+SUM(D74:D75)-SUM(D76:D78)</f>
-        <v/>
-      </c>
-      <c r="E79" s="25">
-        <f>E73+SUM(E74:E75)-SUM(E76:E78)</f>
-        <v/>
-      </c>
-      <c r="F79" s="25">
-        <f>F73+SUM(F74:F75)-SUM(F76:F78)</f>
-        <v/>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>継続＋流入－流出</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　1人当たり月利用量</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>利用者ごとの月間予定量の平均</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>＝　月間サービス量</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="C81" s="27">
-        <f>ROUND(C79*C80,1)</f>
-        <v/>
-      </c>
-      <c r="D81" s="27">
-        <f>ROUND(D79*D80,1)</f>
-        <v/>
-      </c>
-      <c r="E81" s="27">
-        <f>ROUND(E79*E80,1)</f>
-        <v/>
-      </c>
-      <c r="F81" s="27">
-        <f>ROUND(F79*F80,1)</f>
-        <v/>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>利用者数×1人当たり月利用量</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>黄色は入力欄、緑は数式です。継続利用者は前年度の利用者数を自動で繰り越します。流出行はマイナスの人数ではなく、減少する人数を正の数で入力してください（表示は自動でマイナスになります）。令和8年度の基準人数は、村の支給決定者台帳による実利用者数に置き換えてください。現在入っているのは現行計画（第7期）の令和8年度見込量です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="13">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A58:G58"/>
@@ -8849,9 +8876,7 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A70:G70"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A83:G83"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A71:G71"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>

--- a/output/北塩原村_サービス見込量.xlsx
+++ b/output/北塩原村_サービス見込量.xlsx
@@ -2605,7 +2605,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>利用者数</t>
@@ -2613,16 +2613,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>翌年度利用者数 ＝ 前年度継続利用者 ＋ 新規支給決定見込 ＋ 年齢・進学・卒業等による流入 ＋ 施設・病院等からの地域移行 － 介護保険等への移行 － 一般就労・サービス終了 － 死亡・転出・長期入院等</t>
+          <t>必要な利用者数 ＝ 令和８年度末に支援を必要とする方 ＋ 学校卒業・18歳到達による移行 ＋ 障害児入所施設からの移行（18歳から22歳まで） ＋ 施設・病院からの地域生活への移行 ＋ 新たな支給決定の見込み ＋ 転入 － 65歳到達による介護保険への移行 － 40歳から64歳までの特定疾病による介護保険への移行 － 一般就労への移行 － サービスの利用の終了・転出</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>各項を1人単位で加減算する。03・04の各サービスブロックがこの構造</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>計画本文の表5-3と同じ。各項を1人単位で加減算する。03・04の各サービスブロックがこの構造。起点は実利用者ではなく期首の必要者数であり、令和8年度に既に足りていない分を含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>サービス量</t>
